--- a/data/obx_xlsx/AKAST.OL.xlsx
+++ b/data/obx_xlsx/AKAST.OL.xlsx
@@ -14174,11 +14174,26 @@
       <c r="Q68" s="14">
         <v>7494.0</v>
       </c>
-      <c r="R68" s="15"/>
-      <c r="S68" s="15"/>
-      <c r="T68" s="15"/>
-      <c r="U68" s="15"/>
-      <c r="V68" s="15"/>
+      <c r="R68" s="15">
+        <f t="shared" ref="R68:V68" si="1">SUM(R70,R73,R80)</f>
+        <v>6531</v>
+      </c>
+      <c r="S68" s="15">
+        <f t="shared" si="1"/>
+        <v>4610</v>
+      </c>
+      <c r="T68" s="15">
+        <f t="shared" si="1"/>
+        <v>2816</v>
+      </c>
+      <c r="U68" s="15">
+        <f t="shared" si="1"/>
+        <v>1762</v>
+      </c>
+      <c r="V68" s="15">
+        <f t="shared" si="1"/>
+        <v>1551</v>
+      </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="13" t="s">
@@ -15673,13 +15688,16 @@
         <v>14.0</v>
       </c>
       <c r="J100" s="14">
-        <v>399.0</v>
+        <f>399-J101</f>
+        <v>103</v>
       </c>
       <c r="K100" s="14">
-        <v>1560.0</v>
+        <f>1560-K101</f>
+        <v>1238</v>
       </c>
       <c r="L100" s="14">
-        <v>4054.0</v>
+        <f>4054-L101</f>
+        <v>3785</v>
       </c>
       <c r="M100" s="14">
         <v>308.0</v>
